--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" activeTab="3"/>
+    <workbookView windowWidth="20490" windowHeight="7500" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="246">
   <si>
     <t>TestCaseName</t>
   </si>
@@ -919,6 +919,18 @@
   </si>
   <si>
     <t xml:space="preserve">Add Manually </t>
+  </si>
+  <si>
+    <t>123 William St, New York, NY 10038, USA</t>
+  </si>
+  <si>
+    <t>234 W 42nd St, New York, NY 10036, USA</t>
+  </si>
+  <si>
+    <t>321 Middlefield Rd, Menlo Park, CA 94025, USA</t>
+  </si>
+  <si>
+    <t>651 Kapkowski Rd, Elizabeth, NJ 07201, USA</t>
   </si>
 </sst>
 </file>
@@ -1854,10 +1866,10 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2106,11 +2118,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle name="CreateQuote-style" pivot="0" count="2" xr9:uid="{E748266F-4831-4AB8-BBF1-D2F9693D7387}">
+    <tableStyle name="CreateQuote-style" pivot="0" count="2" xr9:uid="{944CA889-1D19-40AC-958F-237CC2FA89CB}">
       <tableStyleElement type="firstRowStripe" dxfId="5"/>
       <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
-    <tableStyle name="CreateQuote-style 2" pivot="0" count="2" xr9:uid="{7B23B2ED-2336-494A-AA3D-81B4B0B19648}">
+    <tableStyle name="CreateQuote-style 2" pivot="0" count="2" xr9:uid="{FF5DE9AE-5DC9-44B4-AA1B-F328E6E23433}">
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
       <tableStyleElement type="secondRowStripe" dxfId="6"/>
     </tableStyle>
@@ -3592,53 +3604,53 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="26" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="26" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="26" t="s">
         <v>44</v>
       </c>
     </row>
@@ -51931,42 +51943,42 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:2">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="26" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:2">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="24" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:2">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="24" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:2">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:2">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>240</v>
       </c>
     </row>
@@ -51979,8 +51991,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="1"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="17.5714285714286" customWidth="1"/>
     <col min="2" max="2" width="43.2857142857143" customWidth="1"/>
@@ -52020,41 +52032,33 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>233</v>
+        <v>234</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>235</v>
+      <c r="A6" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>237</v>
+      <c r="A7" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="24" t="s">
+      <c r="A8" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>240</v>
       </c>
     </row>
@@ -52070,7 +52074,7 @@
   <dimension ref="A1:AZ6"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="20.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="44.7142857142857" customWidth="1"/>
     <col min="2" max="2" width="25.2857142857143" customWidth="1"/>
     <col min="3" max="3" width="23.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="27.1428571428571" customWidth="1"/>
@@ -52397,7 +52401,7 @@
     </row>
     <row r="3" spans="1:52">
       <c r="A3" s="7" t="s">
-        <v>155</v>
+        <v>242</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>156</v>
@@ -52549,7 +52553,7 @@
     </row>
     <row r="4" spans="1:52">
       <c r="A4" s="7" t="s">
-        <v>177</v>
+        <v>243</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>178</v>
@@ -52701,7 +52705,7 @@
     </row>
     <row r="5" spans="1:52">
       <c r="A5" s="7" t="s">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>185</v>
@@ -52853,7 +52857,7 @@
     </row>
     <row r="6" spans="1:52">
       <c r="A6" s="7" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>216</v>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" activeTab="5"/>
+    <workbookView windowWidth="20490" windowHeight="6780" firstSheet="3" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="CreateQuoteConfig" sheetId="4" r:id="rId4"/>
     <sheet name="EditQuoteConfig" sheetId="5" r:id="rId5"/>
     <sheet name="EditQuote" sheetId="6" r:id="rId6"/>
+    <sheet name="CreateEndorsement" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="250">
   <si>
     <t>TestCaseName</t>
   </si>
@@ -932,6 +933,18 @@
   <si>
     <t>651 Kapkowski Rd, Elizabeth, NJ 07201, USA</t>
   </si>
+  <si>
+    <t>56-45 Main St, Flushing, NY 11355, USA</t>
+  </si>
+  <si>
+    <t>435 Phalen Blvd, St Paul, MN 55130, USA</t>
+  </si>
+  <si>
+    <t>654 S Myers St, Los Angeles, CA 90023, USA</t>
+  </si>
+  <si>
+    <t>7650 Sowell Rd, Milton, FL 32570, USA</t>
+  </si>
 </sst>
 </file>
 
@@ -1479,6 +1492,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFF6F8F9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF6F8F9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF6F8F9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
@@ -1489,21 +1517,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF6F8F9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFF6F8F9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF6F8F9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFF6F8F9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1848,10 +1861,10 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1940,10 +1953,10 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2118,11 +2131,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle name="CreateQuote-style" pivot="0" count="2" xr9:uid="{944CA889-1D19-40AC-958F-237CC2FA89CB}">
+    <tableStyle name="CreateQuote-style" pivot="0" count="2" xr9:uid="{31ECCF58-1150-4E25-AA21-361432DBBE48}">
       <tableStyleElement type="firstRowStripe" dxfId="5"/>
       <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
-    <tableStyle name="CreateQuote-style 2" pivot="0" count="2" xr9:uid="{FF5DE9AE-5DC9-44B4-AA1B-F328E6E23433}">
+    <tableStyle name="CreateQuote-style 2" pivot="0" count="2" xr9:uid="{E66BBC20-A18B-4AE2-9967-A48848986E68}">
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
       <tableStyleElement type="secondRowStripe" dxfId="6"/>
     </tableStyle>
@@ -52450,13 +52463,13 @@
       <c r="R3" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="S3" s="16">
-        <v>4</v>
+      <c r="S3" s="17" t="s">
+        <v>181</v>
       </c>
       <c r="T3" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="U3" s="17" t="s">
+      <c r="U3" s="18" t="s">
         <v>162</v>
       </c>
       <c r="V3" s="15">
@@ -52599,13 +52612,13 @@
         <v>0</v>
       </c>
       <c r="Q4" s="10"/>
-      <c r="R4" s="18" t="s">
+      <c r="R4" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="S4" s="18" t="s">
+      <c r="S4" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="T4" s="18" t="s">
+      <c r="T4" s="17" t="s">
         <v>161</v>
       </c>
       <c r="U4" s="19" t="s">
@@ -52760,7 +52773,7 @@
       <c r="T5" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="U5" s="17" t="s">
+      <c r="U5" s="18" t="s">
         <v>188</v>
       </c>
       <c r="V5" s="15">
@@ -52916,7 +52929,7 @@
       <c r="T6" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="U6" s="17" t="s">
+      <c r="U6" s="18" t="s">
         <v>219</v>
       </c>
       <c r="V6" s="15">
@@ -53010,6 +53023,963 @@
         <v>21</v>
       </c>
       <c r="AZ6" s="10"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O3:O6">
+      <formula1>"No,Yes"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AZ7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
+  <cols>
+    <col min="1" max="1" width="44.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="25.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="23.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="27.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="14.4285714285714" customWidth="1"/>
+    <col min="16" max="16" width="26" customWidth="1"/>
+    <col min="27" max="27" width="24.5714285714286" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="142.5" spans="1:52">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52">
+      <c r="A2" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG2" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH2" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="AI2" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ2" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK2" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="AL2" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="AM2" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN2" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="AO2" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP2" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ2" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="AR2" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="AS2" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AT2" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AU2" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="AV2" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="AW2" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="AX2" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="AY2" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="AZ2" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52">
+      <c r="A3" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="8">
+        <v>14300</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="G3" s="10">
+        <v>143000</v>
+      </c>
+      <c r="H3" s="8">
+        <v>14300</v>
+      </c>
+      <c r="I3" s="8">
+        <v>14300</v>
+      </c>
+      <c r="J3" s="15">
+        <v>1</v>
+      </c>
+      <c r="K3" s="15">
+        <v>2015</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="N3" s="8">
+        <v>70</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="S3" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="U3" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="V3" s="15">
+        <v>1950</v>
+      </c>
+      <c r="W3" s="15">
+        <v>850</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y3" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="21">
+        <v>25000</v>
+      </c>
+      <c r="AA3" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC3" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="AD3" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE3" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AF3" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="AG3" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="AH3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN3" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO3" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AP3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ3" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="AR3" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="AS3" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="AT3" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="AU3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ3" s="10"/>
+    </row>
+    <row r="4" spans="1:52">
+      <c r="A4" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="8">
+        <v>14300</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="G4" s="10">
+        <v>146000</v>
+      </c>
+      <c r="H4" s="8">
+        <v>14300</v>
+      </c>
+      <c r="I4" s="8">
+        <v>14300</v>
+      </c>
+      <c r="J4" s="15">
+        <v>1</v>
+      </c>
+      <c r="K4" s="15">
+        <v>2015</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="N4" s="8">
+        <v>70</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="U4" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="V4" s="15">
+        <v>1947</v>
+      </c>
+      <c r="W4" s="15">
+        <v>900</v>
+      </c>
+      <c r="X4" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y4" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="21">
+        <v>25000</v>
+      </c>
+      <c r="AA4" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB4" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AC4" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="AD4" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE4" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AF4" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="AG4" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="AH4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN4" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO4" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AP4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ4" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="AR4" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="AS4" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="AT4" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="AU4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ4" s="10"/>
+    </row>
+    <row r="5" spans="1:52">
+      <c r="A5" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" s="8">
+        <v>14300</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="G5" s="10">
+        <v>147000</v>
+      </c>
+      <c r="H5" s="8">
+        <v>14300</v>
+      </c>
+      <c r="I5" s="8">
+        <v>14300</v>
+      </c>
+      <c r="J5" s="15">
+        <v>1</v>
+      </c>
+      <c r="K5" s="15">
+        <v>2015</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="N5" s="8">
+        <v>70</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="P5" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="S5" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="T5" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="U5" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="V5" s="15">
+        <v>1950</v>
+      </c>
+      <c r="W5" s="15">
+        <v>955</v>
+      </c>
+      <c r="X5" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y5" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="21">
+        <v>25000</v>
+      </c>
+      <c r="AA5" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB5" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="AC5" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="AD5" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE5" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AF5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="AG5" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="AH5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN5" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO5" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AP5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ5" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="AR5" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="AS5" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="AT5" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="AU5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ5" s="10"/>
+    </row>
+    <row r="6" spans="1:52">
+      <c r="A6" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="11">
+        <v>11</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" s="8">
+        <v>14300</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="10">
+        <v>145000</v>
+      </c>
+      <c r="H6" s="8">
+        <v>14300</v>
+      </c>
+      <c r="I6" s="8">
+        <v>14300</v>
+      </c>
+      <c r="J6" s="15">
+        <v>1</v>
+      </c>
+      <c r="K6" s="15">
+        <v>2015</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="N6" s="8">
+        <v>70</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="T6" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="U6" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="V6" s="15">
+        <v>1950</v>
+      </c>
+      <c r="W6" s="15">
+        <v>975</v>
+      </c>
+      <c r="X6" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y6" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="21">
+        <v>25000</v>
+      </c>
+      <c r="AA6" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB6" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="AC6" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="AD6" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE6" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AF6" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="AG6" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="AH6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AK6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN6" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO6" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AP6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ6" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="AR6" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="AS6" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="AT6" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="AU6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AX6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AY6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ6" s="10"/>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" firstSheet="6" activeTab="10"/>
+    <workbookView windowWidth="20490" windowHeight="7500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="266">
   <si>
     <t>TestCaseName</t>
   </si>
@@ -897,10 +897,13 @@
     <t>Upload</t>
   </si>
   <si>
+    <t xml:space="preserve">Add Manually </t>
+  </si>
+  <si>
     <t xml:space="preserve">Upload Path </t>
   </si>
   <si>
-    <t>C:\Users\HP\Downloads\CPI_Final\src\test\resources\testdata\LocationsCounty.xlsx</t>
+    <t>src\test\resources\testdata\LocationsCounty.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Agent </t>
@@ -922,9 +925,6 @@
   </si>
   <si>
     <t>New York</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Add Manually </t>
   </si>
   <si>
     <t>123 William St, New York, NY 10038, USA</t>
@@ -990,13 +990,13 @@
     <t>ARCHKS2471829</t>
   </si>
   <si>
-    <t>ARCHNY2472168</t>
+    <t>ARCHNY2472181</t>
   </si>
   <si>
-    <t>ARCH75887,ARCH75886,ARCH75885</t>
+    <t>ARCH76004, ARCH76003, ARCH76002</t>
   </si>
   <si>
-    <t>ARCH75884, ARCH75881</t>
+    <t>ARCH76000, ARCH75999</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1021,7 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="18"/>
       <color rgb="FF002A67"/>
       <name val="Inter"/>
       <charset val="134"/>
@@ -3749,11 +3749,11 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="19.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="38.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" t="s">
         <v>254</v>
       </c>
@@ -3782,11 +3782,11 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="18.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="29.8571428571429" customWidth="1"/>
     <col min="3" max="3" width="38.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" t="s">
         <v>254</v>
       </c>
@@ -52140,8 +52140,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="15" customHeight="1" outlineLevelCol="1"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="15.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="44.1428571428571" customWidth="1"/>
@@ -52171,41 +52171,44 @@
         <v>229</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:2">
+    <row r="4" customHeight="1" spans="1:3">
       <c r="A4" s="15" t="s">
         <v>230</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>231</v>
       </c>
+      <c r="C4" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="5" customHeight="1" spans="1:2">
       <c r="A5" s="34" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:2">
       <c r="A6" s="31" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:2">
       <c r="A7" s="31" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:2">
       <c r="A8" s="33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B8" s="31" t="s">
         <v>11</v>
@@ -52213,10 +52216,10 @@
     </row>
     <row r="9" customHeight="1" spans="1:2">
       <c r="A9" s="31" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -52264,28 +52267,28 @@
         <v>230</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="31" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="31" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B7" s="31" t="s">
         <v>11</v>
@@ -52293,10 +52296,10 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="31" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" activeTab="3"/>
+    <workbookView windowWidth="20490" windowHeight="6780" firstSheet="6" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -990,13 +990,13 @@
     <t>ARCHKS2471829</t>
   </si>
   <si>
-    <t>ARCHNY2472181</t>
+    <t>ARCHNY2472203</t>
   </si>
   <si>
-    <t>ARCH76004, ARCH76003, ARCH76002</t>
+    <t>ARCH76364, ARCH76362, ARCH76360, ARCH76358</t>
   </si>
   <si>
-    <t>ARCH76000, ARCH75999</t>
+    <t>ARCH76367, ARCH76366</t>
   </si>
 </sst>
 </file>
@@ -2231,11 +2231,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle name="CreateQuote-style" pivot="0" count="2" xr9:uid="{F6CE7AA6-2DAB-422C-A311-9F4199F71445}">
+    <tableStyle name="CreateQuote-style" pivot="0" count="2" xr9:uid="{F8CD9ACE-65BD-458E-90A4-2F741191FCB3}">
       <tableStyleElement type="firstRowStripe" dxfId="5"/>
       <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
-    <tableStyle name="CreateQuote-style 2" pivot="0" count="2" xr9:uid="{BE2D46D9-E12B-4FAB-8A86-6698FA77D229}">
+    <tableStyle name="CreateQuote-style 2" pivot="0" count="2" xr9:uid="{8D493152-D472-41AF-823A-77D1A08C8E74}">
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
       <tableStyleElement type="secondRowStripe" dxfId="6"/>
     </tableStyle>

--- a/src/test/resources/testdata/TestData.xlsx
+++ b/src/test/resources/testdata/TestData.xlsx
@@ -4,21 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6780" firstSheet="6" activeTab="10"/>
+    <workbookView windowWidth="20490" windowHeight="6780" firstSheet="5" activeTab="10"/>
   </bookViews>
   <sheets>
-    <sheet name="LoginData" sheetId="1" r:id="rId1"/>
-    <sheet name="UserData" sheetId="2" r:id="rId2"/>
-    <sheet name="CreateQuote" sheetId="3" r:id="rId3"/>
-    <sheet name="CreateQuoteConfig" sheetId="4" r:id="rId4"/>
-    <sheet name="EditQuoteConfig" sheetId="5" r:id="rId5"/>
-    <sheet name="EditQuote" sheetId="6" r:id="rId6"/>
-    <sheet name="CreateEndorsement" sheetId="8" r:id="rId7"/>
-    <sheet name="EditEndorsement" sheetId="9" r:id="rId8"/>
-    <sheet name="Transaction" sheetId="10" r:id="rId9"/>
-    <sheet name="Invoice" sheetId="11" r:id="rId10"/>
-    <sheet name="CreateFlatCancel" sheetId="12" r:id="rId11"/>
-    <sheet name="EditFlatCancel" sheetId="13" r:id="rId12"/>
+    <sheet name="UserData" sheetId="2" r:id="rId1"/>
+    <sheet name="CreateQuote" sheetId="3" r:id="rId2"/>
+    <sheet name="CreateQuoteConfig" sheetId="4" r:id="rId3"/>
+    <sheet name="EditQuoteConfig" sheetId="5" r:id="rId4"/>
+    <sheet name="EditQuote" sheetId="6" r:id="rId5"/>
+    <sheet name="CreateEndorsement" sheetId="8" r:id="rId6"/>
+    <sheet name="EditEndorsement" sheetId="9" r:id="rId7"/>
+    <sheet name="Transaction" sheetId="10" r:id="rId8"/>
+    <sheet name="Invoice" sheetId="11" r:id="rId9"/>
+    <sheet name="CreateFlatCancel" sheetId="12" r:id="rId10"/>
+    <sheet name="EditFlatCancel" sheetId="13" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,126 +37,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="227">
   <si>
-    <t>TestCaseName</t>
-  </si>
-  <si>
-    <t>Description</t>
+    <t>UserType</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
     <t>Password</t>
-  </si>
-  <si>
-    <t>ExpectedResult</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>TC_Login_001</t>
-  </si>
-  <si>
-    <t>Valid Admin Login</t>
-  </si>
-  <si>
-    <t>admin@cpiai.com</t>
-  </si>
-  <si>
-    <t>Admin@123</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>TC_Login_002</t>
-  </si>
-  <si>
-    <t>Invalid Password</t>
-  </si>
-  <si>
-    <t>WrongPassword</t>
-  </si>
-  <si>
-    <t>failure</t>
-  </si>
-  <si>
-    <t>TC_Login_003</t>
-  </si>
-  <si>
-    <t>Invalid Email</t>
-  </si>
-  <si>
-    <t>invalid@cpiai.com</t>
-  </si>
-  <si>
-    <t>TC_Login_004</t>
-  </si>
-  <si>
-    <t>Empty Email</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>TC_Login_005</t>
-  </si>
-  <si>
-    <t>Empty Password</t>
-  </si>
-  <si>
-    <t>TC_Login_006</t>
-  </si>
-  <si>
-    <t>Empty Credentials</t>
-  </si>
-  <si>
-    <t>TC_Login_007</t>
-  </si>
-  <si>
-    <t>Invalid Email Format</t>
-  </si>
-  <si>
-    <t>admincpiai.com</t>
-  </si>
-  <si>
-    <t>TC_Login_008</t>
-  </si>
-  <si>
-    <t>SQL Injection Test</t>
-  </si>
-  <si>
-    <t>admin@cpiai.com' OR '1'='1</t>
-  </si>
-  <si>
-    <t>TC_Login_009</t>
-  </si>
-  <si>
-    <t>XSS Test</t>
-  </si>
-  <si>
-    <t>&lt;script&gt;alert('xss')&lt;/script&gt;</t>
-  </si>
-  <si>
-    <t>TC_Login_010</t>
-  </si>
-  <si>
-    <t>Special Characters</t>
-  </si>
-  <si>
-    <t>Admin@123!@#$%</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>UserType</t>
   </si>
   <si>
     <t>Role</t>
@@ -169,31 +57,16 @@
     <t>Admin</t>
   </si>
   <si>
+    <t>abhishek.byahut@attri.ai</t>
+  </si>
+  <si>
+    <t>Attri@123</t>
+  </si>
+  <si>
     <t>Administrator</t>
   </si>
   <si>
     <t>Active</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>user@cpiai.com</t>
-  </si>
-  <si>
-    <t>User@123</t>
-  </si>
-  <si>
-    <t>Standard User</t>
-  </si>
-  <si>
-    <t>Guest</t>
-  </si>
-  <si>
-    <t>guest@cpiai.com</t>
-  </si>
-  <si>
-    <t>Guest@123</t>
   </si>
   <si>
     <t>From IPP Rewrite Speadsheet</t>
@@ -681,6 +554,9 @@
     <t>RCV</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>Louisville</t>
   </si>
   <si>
@@ -714,6 +590,9 @@
     <t>78247</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t xml:space="preserve">NHR Property Management, LLC </t>
   </si>
   <si>
@@ -739,6 +618,9 @@
   </si>
   <si>
     <t>ESCROW</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
   <si>
     <t>Lewisport</t>
@@ -990,13 +872,13 @@
     <t>ARCHKS2471829</t>
   </si>
   <si>
-    <t>ARCHNY2472203</t>
+    <t>ARCHTX2471774</t>
   </si>
   <si>
-    <t>ARCH76364, ARCH76362, ARCH76360, ARCH76358</t>
+    <t>ARCH73245, ARCH67986</t>
   </si>
   <si>
-    <t>ARCH76367, ARCH76366</t>
+    <t>ARCH76001, ARCH72653, ARCH67989</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +893,7 @@
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="179" formatCode="0.000000_);[Red]\(0.000000\)"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1122,19 +1004,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -1289,7 +1158,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1342,12 +1211,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFCC"/>
         <bgColor rgb="FFCCFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3366FF"/>
-        <bgColor rgb="FF3366FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1766,133 +1629,133 @@
     <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2086,8 +1949,8 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2466,237 +2329,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1000"/>
-  <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="15" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="A1:E1000"/>
+  <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="15" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="14.2857142857143" customWidth="1"/>
-    <col min="2" max="2" width="17.2857142857143" customWidth="1"/>
-    <col min="3" max="3" width="23.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="16.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="14.7142857142857" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="26" width="8.71428571428571" customWidth="1"/>
+    <col min="1" max="1" width="8.71428571428571" customWidth="1"/>
+    <col min="2" max="2" width="27.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="27.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="6" max="26" width="8.71428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:6">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="75" t="s">
+    </row>
+    <row r="2" ht="15.75" spans="1:5">
+      <c r="A2" s="34" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="76" t="s">
+      <c r="B2" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="76" t="s">
+      <c r="C2" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="D2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="E2" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="76" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="76" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="76" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="76" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="76" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="76" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="76" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="76" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="76" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="76" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="76" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="76" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="76" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="76" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="76" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="76" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="76" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="76" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="76" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="76" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="76" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="76" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="76" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="76" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="76" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="76" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="76" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="76" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="76" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="76" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="76" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="76" t="s">
-        <v>38</v>
-      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -3679,6 +3369,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" display="Attri@123"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="1" orientation="landscape"/>
   <headerFooter/>
@@ -3688,54 +3381,29 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="1"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="28.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="38.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" ht="23.25" spans="1:3">
       <c r="A1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" spans="2:2">
-      <c r="B2" s="5" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2">
-      <c r="B3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2">
-      <c r="B4" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2">
-      <c r="B6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
-      <c r="B7" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" t="s">
-        <v>262</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" spans="3:3">
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3749,52 +3417,19 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="38.5714285714286" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="23.25" spans="1:3">
-      <c r="A1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="2" spans="3:3">
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" spans="3:3">
-      <c r="C3" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="2"/>
-  <cols>
     <col min="2" max="2" width="29.8571428571429" customWidth="1"/>
     <col min="3" max="3" width="38.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.25" spans="1:3">
       <c r="A1" t="s">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="3:3">
@@ -3810,1075 +3445,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E1000"/>
-  <sheetFormatPr defaultColWidth="14.4285714285714" defaultRowHeight="15" customHeight="1" outlineLevelCol="4"/>
-  <cols>
-    <col min="1" max="1" width="8.71428571428571" customWidth="1"/>
-    <col min="2" max="2" width="15.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="12.2857142857143" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="26" width="8.71428571428571" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="74" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="74" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="74" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AZ1000"/>
@@ -4929,7 +3495,7 @@
       <c r="B1" s="36"/>
       <c r="C1" s="36"/>
       <c r="D1" s="37" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="E1" s="36"/>
       <c r="F1" s="36"/>
@@ -4982,330 +3548,330 @@
     </row>
     <row r="2" ht="114" spans="1:52">
       <c r="A2" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="X2" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z2" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB2" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC2" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD2" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE2" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG2" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH2" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI2" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ2" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK2" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL2" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM2" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN2" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO2" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP2" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ2" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="AR2" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="AS2" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="AT2" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="AU2" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="AV2" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="AW2" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="AX2" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="AY2" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="K2" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="L2" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="M2" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="N2" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="O2" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="P2" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q2" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="R2" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="S2" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="T2" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="U2" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="V2" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="W2" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="X2" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y2" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z2" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA2" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB2" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC2" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD2" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE2" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF2" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG2" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH2" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="AI2" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ2" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK2" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL2" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM2" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN2" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="AO2" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP2" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ2" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR2" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS2" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="AT2" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="AU2" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="AV2" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="AW2" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="AX2" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="AY2" s="38" t="s">
-        <v>103</v>
-      </c>
       <c r="AZ2" s="38" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:52">
       <c r="A3" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="I3" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J3" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="M3" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="N3" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="O3" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="P3" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q3" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="R3" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="T3" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="U3" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="V3" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="W3" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="X3" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y3" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z3" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA3" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB3" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC3" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD3" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE3" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF3" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG3" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH3" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI3" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ3" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK3" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="AL3" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM3" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="AN3" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO3" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="AP3" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ3" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="AR3" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="AS3" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="AT3" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="AU3" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="AV3" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="AW3" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="AX3" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="AY3" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="J3" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="K3" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="L3" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="M3" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="N3" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="O3" s="55" t="s">
-        <v>118</v>
-      </c>
-      <c r="P3" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q3" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="R3" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="S3" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="U3" s="42" t="s">
-        <v>124</v>
-      </c>
-      <c r="V3" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="W3" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="X3" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y3" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z3" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA3" s="42" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB3" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC3" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="AD3" s="42" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE3" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="AF3" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG3" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH3" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="AI3" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ3" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="AK3" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="AL3" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="AM3" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="AN3" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="AO3" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="AP3" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="AQ3" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="AR3" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="AS3" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="AT3" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="AU3" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="AV3" s="42" t="s">
-        <v>151</v>
-      </c>
-      <c r="AW3" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="AX3" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="AY3" s="42" t="s">
-        <v>154</v>
-      </c>
       <c r="AZ3" s="36" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:52">
       <c r="A4" s="44" t="s">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="36" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="E4" s="45">
         <v>14300</v>
@@ -5329,32 +3895,32 @@
         <v>2015</v>
       </c>
       <c r="L4" s="57" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M4" s="57" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N4" s="45">
         <v>70</v>
       </c>
       <c r="O4" s="58" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="P4" s="59" t="b">
         <v>0</v>
       </c>
       <c r="Q4" s="57"/>
       <c r="R4" s="60" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="S4" s="61">
         <v>4</v>
       </c>
       <c r="T4" s="60" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U4" s="62" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="V4" s="56">
         <v>1950</v>
@@ -5363,7 +3929,7 @@
         <v>850</v>
       </c>
       <c r="X4" s="57" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y4" s="67">
         <v>1</v>
@@ -5372,92 +3938,92 @@
         <v>25000</v>
       </c>
       <c r="AA4" s="69" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB4" s="44" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="AC4" s="70" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD4" s="57" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE4" s="57" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF4" s="57" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG4" s="57" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN4" s="57" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO4" s="57" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ4" s="57" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR4" s="57" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS4" s="57" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT4" s="57" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY4" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ4" s="57"/>
     </row>
     <row r="5" spans="1:52">
       <c r="A5" s="44" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="C5" s="36"/>
       <c r="D5" s="43" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="E5" s="45">
         <v>14300</v>
@@ -5481,32 +4047,32 @@
         <v>2015</v>
       </c>
       <c r="L5" s="57" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M5" s="57" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N5" s="45">
         <v>70</v>
       </c>
       <c r="O5" s="58" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="P5" s="59" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="57"/>
       <c r="R5" s="63" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="S5" s="63" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T5" s="63" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U5" s="64" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="V5" s="56">
         <v>1947</v>
@@ -5515,7 +4081,7 @@
         <v>900</v>
       </c>
       <c r="X5" s="57" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y5" s="67">
         <v>1</v>
@@ -5524,92 +4090,92 @@
         <v>25000</v>
       </c>
       <c r="AA5" s="69" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB5" s="44" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="AC5" s="70" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD5" s="57" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE5" s="57" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF5" s="57" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG5" s="57" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN5" s="57" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO5" s="57" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ5" s="57" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR5" s="57" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS5" s="57" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT5" s="57" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY5" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ5" s="57"/>
     </row>
     <row r="6" spans="1:52">
       <c r="A6" s="44" t="s">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="C6" s="36"/>
       <c r="D6" s="43" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="E6" s="45">
         <v>14300</v>
@@ -5633,32 +4199,32 @@
         <v>2015</v>
       </c>
       <c r="L6" s="57" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M6" s="57" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N6" s="45">
         <v>70</v>
       </c>
       <c r="O6" s="58" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="P6" s="59" t="b">
         <v>0</v>
       </c>
       <c r="Q6" s="57"/>
       <c r="R6" s="60" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="S6" s="60" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T6" s="60" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U6" s="62" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="V6" s="56">
         <v>1950</v>
@@ -5667,7 +4233,7 @@
         <v>955</v>
       </c>
       <c r="X6" s="57" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y6" s="67">
         <v>1</v>
@@ -5676,92 +4242,92 @@
         <v>25000</v>
       </c>
       <c r="AA6" s="69" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB6" s="44" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="AC6" s="70" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD6" s="57" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE6" s="57" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF6" s="57" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG6" s="57" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN6" s="57" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO6" s="57" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ6" s="57" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR6" s="57" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS6" s="57" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT6" s="57" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY6" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ6" s="57"/>
     </row>
     <row r="7" spans="1:52">
       <c r="A7" s="44" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="C7" s="36"/>
       <c r="D7" s="36" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="E7" s="45">
         <v>14300</v>
@@ -5785,32 +4351,32 @@
         <v>2015</v>
       </c>
       <c r="L7" s="57" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M7" s="57" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N7" s="45">
         <v>70</v>
       </c>
       <c r="O7" s="58" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="P7" s="59" t="b">
         <v>0</v>
       </c>
       <c r="Q7" s="57"/>
       <c r="R7" s="63" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="S7" s="63" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T7" s="63" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U7" s="64" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="V7" s="56">
         <v>1951</v>
@@ -5819,7 +4385,7 @@
         <v>758</v>
       </c>
       <c r="X7" s="57" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y7" s="67">
         <v>1</v>
@@ -5828,92 +4394,92 @@
         <v>25000</v>
       </c>
       <c r="AA7" s="69" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB7" s="44" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="AC7" s="70" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD7" s="57" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE7" s="57" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF7" s="57" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG7" s="57" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN7" s="57" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO7" s="57" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ7" s="57" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR7" s="57" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS7" s="57" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT7" s="57" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY7" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ7" s="57"/>
     </row>
     <row r="8" spans="1:52">
       <c r="A8" s="44" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="C8" s="36"/>
       <c r="D8" s="36" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="E8" s="45">
         <v>14300</v>
@@ -5937,32 +4503,32 @@
         <v>2015</v>
       </c>
       <c r="L8" s="57" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M8" s="57" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N8" s="45">
         <v>70</v>
       </c>
       <c r="O8" s="58" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="P8" s="59" t="b">
         <v>0</v>
       </c>
       <c r="Q8" s="57"/>
       <c r="R8" s="60" t="s">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="S8" s="60" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T8" s="60" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U8" s="62" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="V8" s="56">
         <v>1953</v>
@@ -5971,7 +4537,7 @@
         <v>919</v>
       </c>
       <c r="X8" s="57" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y8" s="67">
         <v>1</v>
@@ -5980,92 +4546,92 @@
         <v>25000</v>
       </c>
       <c r="AA8" s="69" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB8" s="44" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="AC8" s="70" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD8" s="57" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE8" s="57" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF8" s="57" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG8" s="57" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN8" s="57" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO8" s="57" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ8" s="57" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR8" s="57" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS8" s="57" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT8" s="57" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY8" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ8" s="57"/>
     </row>
     <row r="9" spans="1:52">
       <c r="A9" s="44" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>201</v>
+        <v>162</v>
       </c>
       <c r="C9" s="36"/>
       <c r="D9" s="36" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="E9" s="45">
         <v>14300</v>
@@ -6089,32 +4655,32 @@
         <v>2015</v>
       </c>
       <c r="L9" s="57" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M9" s="57" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N9" s="45">
         <v>70</v>
       </c>
       <c r="O9" s="58" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="P9" s="59" t="b">
         <v>0</v>
       </c>
       <c r="Q9" s="57"/>
       <c r="R9" s="63" t="s">
-        <v>202</v>
+        <v>163</v>
       </c>
       <c r="S9" s="63" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T9" s="63" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U9" s="64" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="V9" s="56">
         <v>1950</v>
@@ -6123,7 +4689,7 @@
         <v>792</v>
       </c>
       <c r="X9" s="57" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y9" s="67">
         <v>1</v>
@@ -6132,92 +4698,92 @@
         <v>25000</v>
       </c>
       <c r="AA9" s="69" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB9" s="44" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="AC9" s="70" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD9" s="57" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE9" s="57" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF9" s="57" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG9" s="57" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN9" s="57" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO9" s="57" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ9" s="57" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR9" s="57" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS9" s="57" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT9" s="57" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY9" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ9" s="57"/>
     </row>
     <row r="10" spans="1:52">
       <c r="A10" s="44" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="C10" s="36"/>
       <c r="D10" s="36" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="E10" s="45">
         <v>14300</v>
@@ -6241,32 +4807,32 @@
         <v>2015</v>
       </c>
       <c r="L10" s="57" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M10" s="57" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N10" s="45">
         <v>70</v>
       </c>
       <c r="O10" s="58" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="P10" s="59" t="b">
         <v>0</v>
       </c>
       <c r="Q10" s="57"/>
       <c r="R10" s="60" t="s">
-        <v>207</v>
+        <v>168</v>
       </c>
       <c r="S10" s="60" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T10" s="60" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U10" s="62" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="V10" s="56">
         <v>1955</v>
@@ -6275,7 +4841,7 @@
         <v>1040</v>
       </c>
       <c r="X10" s="57" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y10" s="67">
         <v>1</v>
@@ -6284,92 +4850,92 @@
         <v>25000</v>
       </c>
       <c r="AA10" s="69" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB10" s="44" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="AC10" s="70" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD10" s="57" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE10" s="57" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF10" s="57" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG10" s="57" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN10" s="57" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO10" s="57" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ10" s="57" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR10" s="57" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS10" s="57" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT10" s="57" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY10" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ10" s="57"/>
     </row>
     <row r="11" spans="1:52">
       <c r="A11" s="44" t="s">
-        <v>210</v>
+        <v>171</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="C11" s="36"/>
       <c r="D11" s="36" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="E11" s="45">
         <v>14300</v>
@@ -6393,32 +4959,32 @@
         <v>2015</v>
       </c>
       <c r="L11" s="57" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M11" s="57" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N11" s="45">
         <v>70</v>
       </c>
       <c r="O11" s="58" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="P11" s="59" t="b">
         <v>0</v>
       </c>
       <c r="Q11" s="57"/>
       <c r="R11" s="63" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="S11" s="63" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T11" s="63" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U11" s="64" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
       <c r="V11" s="56">
         <v>1955</v>
@@ -6427,7 +4993,7 @@
         <v>1366</v>
       </c>
       <c r="X11" s="57" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y11" s="67">
         <v>1</v>
@@ -6436,94 +5002,94 @@
         <v>25000</v>
       </c>
       <c r="AA11" s="69" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB11" s="44" t="s">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="AC11" s="70" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD11" s="57" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE11" s="57" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF11" s="57" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG11" s="57" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN11" s="57" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO11" s="57" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ11" s="57" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR11" s="57" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS11" s="57" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT11" s="57" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY11" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ11" s="57"/>
     </row>
     <row r="12" spans="1:52">
       <c r="A12" s="44" t="s">
-        <v>215</v>
+        <v>176</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="C12" s="48">
         <v>10</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="E12" s="45">
         <v>14300</v>
@@ -6547,16 +5113,16 @@
         <v>2015</v>
       </c>
       <c r="L12" s="57" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M12" s="57" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N12" s="45">
         <v>70</v>
       </c>
       <c r="O12" s="58" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="P12" s="59" t="b">
         <v>0</v>
@@ -6565,16 +5131,16 @@
         <v>0</v>
       </c>
       <c r="R12" s="60" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="S12" s="60" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T12" s="60" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U12" s="62" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="V12" s="56">
         <v>1950</v>
@@ -6583,7 +5149,7 @@
         <v>975</v>
       </c>
       <c r="X12" s="57" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y12" s="67">
         <v>1</v>
@@ -6592,94 +5158,94 @@
         <v>25000</v>
       </c>
       <c r="AA12" s="69" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB12" s="44" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="AC12" s="70" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD12" s="57" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE12" s="57" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF12" s="57" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG12" s="57" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN12" s="57" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO12" s="57" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ12" s="57" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR12" s="57" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS12" s="57" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT12" s="57" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY12" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ12" s="57"/>
     </row>
     <row r="13" spans="1:52">
       <c r="A13" s="44" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="C13" s="48">
         <v>12</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="E13" s="45">
         <v>14300</v>
@@ -6703,16 +5269,16 @@
         <v>2015</v>
       </c>
       <c r="L13" s="57" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M13" s="57" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N13" s="45">
         <v>70</v>
       </c>
       <c r="O13" s="58" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="P13" s="59" t="b">
         <v>0</v>
@@ -6721,16 +5287,16 @@
         <v>1</v>
       </c>
       <c r="R13" s="65" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
       <c r="S13" s="65" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T13" s="65" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U13" s="66" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="V13" s="56">
         <v>1948</v>
@@ -6739,7 +5305,7 @@
         <v>1335</v>
       </c>
       <c r="X13" s="57" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y13" s="67">
         <v>2</v>
@@ -6748,79 +5314,79 @@
         <v>25000</v>
       </c>
       <c r="AA13" s="69" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB13" s="71" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="AC13" s="70" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD13" s="57" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE13" s="57" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF13" s="57" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG13" s="57" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN13" s="57" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO13" s="57" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ13" s="57" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR13" s="57" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS13" s="57" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT13" s="57" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY13" s="57" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ13" s="57"/>
     </row>
@@ -52135,7 +50701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -52149,7 +50715,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:2">
       <c r="A1" s="15" t="s">
-        <v>226</v>
+        <v>187</v>
       </c>
       <c r="B1" s="15">
         <v>150</v>
@@ -52157,7 +50723,7 @@
     </row>
     <row r="2" customHeight="1" spans="1:2">
       <c r="A2" s="15" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
       <c r="B2" s="15">
         <v>120</v>
@@ -52165,61 +50731,61 @@
     </row>
     <row r="3" customHeight="1" spans="1:2">
       <c r="A3" s="15" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>229</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:3">
       <c r="A4" s="15" t="s">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="C4" t="s">
-        <v>232</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:2">
       <c r="A5" s="34" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:2">
       <c r="A6" s="31" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:2">
       <c r="A7" s="31" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:2">
       <c r="A8" s="33" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:2">
       <c r="A9" s="31" t="s">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -52228,7 +50794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B8"/>
@@ -52240,7 +50806,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="15" t="s">
-        <v>226</v>
+        <v>187</v>
       </c>
       <c r="B1" s="15">
         <v>190</v>
@@ -52248,7 +50814,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="15" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
       <c r="B2" s="15">
         <v>130</v>
@@ -52256,50 +50822,50 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="15" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>229</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="15" t="s">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>232</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="31" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="31" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="33" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="31" t="s">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -52308,7 +50874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AZ6"/>
@@ -52325,330 +50891,330 @@
   <sheetData>
     <row r="1" ht="142.5" spans="1:52">
       <c r="A1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="AR1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="AS1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="AT1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="AU1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="AV1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="AW1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="AX1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="AY1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="K1" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P1" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q1" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="U1" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="V1" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="W1" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="X1" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y1" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z1" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB1" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC1" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD1" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE1" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF1" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG1" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH1" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="AI1" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ1" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK1" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL1" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM1" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN1" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="AO1" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP1" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ1" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR1" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS1" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AT1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="AU1" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="AV1" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="AW1" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="AX1" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="AY1" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="AZ1" s="7" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:52">
       <c r="A2" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="U2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="V2" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="W2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA2" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC2" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD2" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE2" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF2" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG2" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH2" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI2" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK2" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AL2" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="AN2" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO2" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AP2" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="AR2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="AS2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="AT2" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="AU2" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="AV2" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="AW2" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="AX2" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="AY2" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="U2" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="V2" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y2" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z2" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA2" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB2" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC2" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="AD2" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE2" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="AF2" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG2" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH2" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="AI2" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ2" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="AK2" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="AL2" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="AM2" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="AN2" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="AO2" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="AP2" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AQ2" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="AR2" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="AS2" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="AT2" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="AU2" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="AV2" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="AW2" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="AX2" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="AY2" s="12" t="s">
-        <v>154</v>
-      </c>
       <c r="AZ2" s="12" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:52">
       <c r="A3" s="15" t="s">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="E3" s="16">
         <v>14300</v>
@@ -52672,32 +51238,32 @@
         <v>2015</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N3" s="16">
         <v>70</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="P3" s="17" t="b">
         <v>0</v>
       </c>
       <c r="Q3" s="17"/>
       <c r="R3" s="23" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T3" s="23" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U3" s="25" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="V3" s="22">
         <v>1950</v>
@@ -52706,7 +51272,7 @@
         <v>850</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y3" s="27">
         <v>1</v>
@@ -52715,92 +51281,92 @@
         <v>25000</v>
       </c>
       <c r="AA3" s="29" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB3" s="15" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="AC3" s="22" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD3" s="17" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE3" s="17" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF3" s="17" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG3" s="17" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN3" s="17" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO3" s="17" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ3" s="17" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR3" s="17" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS3" s="17" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT3" s="17" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ3" s="17"/>
     </row>
     <row r="4" spans="1:52">
       <c r="A4" s="15" t="s">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="13" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="E4" s="16">
         <v>14300</v>
@@ -52824,32 +51390,32 @@
         <v>2015</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N4" s="16">
         <v>70</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="P4" s="17" t="b">
         <v>0</v>
       </c>
       <c r="Q4" s="17"/>
       <c r="R4" s="24" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T4" s="24" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U4" s="26" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="V4" s="22">
         <v>1947</v>
@@ -52858,7 +51424,7 @@
         <v>900</v>
       </c>
       <c r="X4" s="17" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y4" s="27">
         <v>1</v>
@@ -52867,92 +51433,92 @@
         <v>25000</v>
       </c>
       <c r="AA4" s="29" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="AC4" s="22" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD4" s="17" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE4" s="17" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF4" s="17" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG4" s="17" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN4" s="17" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO4" s="17" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ4" s="17" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR4" s="17" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS4" s="17" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT4" s="17" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ4" s="17"/>
     </row>
     <row r="5" spans="1:52">
       <c r="A5" s="15" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="13" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="E5" s="16">
         <v>14300</v>
@@ -52976,32 +51542,32 @@
         <v>2015</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N5" s="16">
         <v>70</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="P5" s="17" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="23" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T5" s="23" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U5" s="25" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="V5" s="22">
         <v>1950</v>
@@ -53010,7 +51576,7 @@
         <v>955</v>
       </c>
       <c r="X5" s="17" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y5" s="27">
         <v>1</v>
@@ -53019,94 +51585,94 @@
         <v>25000</v>
       </c>
       <c r="AA5" s="29" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB5" s="15" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="AC5" s="22" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD5" s="17" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE5" s="17" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF5" s="17" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG5" s="17" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN5" s="17" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO5" s="17" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ5" s="17" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR5" s="17" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS5" s="17" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT5" s="17" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ5" s="17"/>
     </row>
     <row r="6" spans="1:52">
       <c r="A6" s="15" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="C6" s="18">
         <v>10</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="E6" s="16">
         <v>14300</v>
@@ -53130,16 +51696,16 @@
         <v>2015</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N6" s="16">
         <v>70</v>
       </c>
       <c r="O6" s="16" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="P6" s="17" t="b">
         <v>0</v>
@@ -53148,16 +51714,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="23" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T6" s="23" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="V6" s="22">
         <v>1950</v>
@@ -53166,7 +51732,7 @@
         <v>975</v>
       </c>
       <c r="X6" s="17" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y6" s="27">
         <v>1</v>
@@ -53175,81 +51741,1041 @@
         <v>25000</v>
       </c>
       <c r="AA6" s="29" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB6" s="15" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="AC6" s="22" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD6" s="17" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE6" s="17" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF6" s="17" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG6" s="17" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN6" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AO6" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="AP6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ6" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR6" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="AS6" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="AT6" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AV6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AY6" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ6" s="17"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O3:O6">
+      <formula1>"No,Yes"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AZ7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
+  <cols>
+    <col min="1" max="1" width="44.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="25.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="23.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="27.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="14.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="12.2857142857143" customWidth="1"/>
+    <col min="16" max="16" width="26" customWidth="1"/>
+    <col min="27" max="27" width="24.5714285714286" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="142.5" spans="1:52">
+      <c r="A1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="19" t="s">
         <v>21</v>
       </c>
+      <c r="L1" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AS1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AT1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AU1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AV1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AW1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AX1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AZ1" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52">
+      <c r="A2" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="U2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="V2" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="W2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA2" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC2" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD2" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE2" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF2" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG2" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH2" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI2" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK2" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AL2" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="AN2" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO2" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AP2" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ2" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="AR2" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS2" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AT2" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="AU2" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AV2" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="AW2" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX2" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="AY2" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="AZ2" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52">
+      <c r="A3" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="16">
+        <v>14300</v>
+      </c>
+      <c r="F3" s="30">
+        <v>0.25</v>
+      </c>
+      <c r="G3" s="17">
+        <v>143000</v>
+      </c>
+      <c r="H3" s="16">
+        <v>14300</v>
+      </c>
+      <c r="I3" s="16">
+        <v>14300</v>
+      </c>
+      <c r="J3" s="22">
+        <v>1</v>
+      </c>
+      <c r="K3" s="22">
+        <v>2015</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="N3" s="16">
+        <v>70</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="P3" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="S3" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="T3" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="U3" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="V3" s="22">
+        <v>1950</v>
+      </c>
+      <c r="W3" s="22">
+        <v>850</v>
+      </c>
+      <c r="X3" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y3" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="28">
+        <v>25000</v>
+      </c>
+      <c r="AA3" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB3" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD3" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE3" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF3" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG3" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN3" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AO3" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="AP3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ3" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR3" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="AS3" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="AT3" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AV3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AY3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ3" s="17"/>
+    </row>
+    <row r="4" spans="1:52">
+      <c r="A4" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="16">
+        <v>14300</v>
+      </c>
+      <c r="F4" s="30">
+        <v>0.25</v>
+      </c>
+      <c r="G4" s="17">
+        <v>146000</v>
+      </c>
+      <c r="H4" s="16">
+        <v>14300</v>
+      </c>
+      <c r="I4" s="16">
+        <v>14300</v>
+      </c>
+      <c r="J4" s="22">
+        <v>1</v>
+      </c>
+      <c r="K4" s="22">
+        <v>2015</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="N4" s="16">
+        <v>70</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="P4" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="S4" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="T4" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="U4" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="V4" s="22">
+        <v>1947</v>
+      </c>
+      <c r="W4" s="22">
+        <v>900</v>
+      </c>
+      <c r="X4" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y4" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="28">
+        <v>25000</v>
+      </c>
+      <c r="AA4" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB4" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="AC4" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD4" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE4" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF4" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG4" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN4" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AO4" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="AP4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ4" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR4" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="AS4" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="AT4" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AV4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AY4" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ4" s="17"/>
+    </row>
+    <row r="5" spans="1:52">
+      <c r="A5" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="16">
+        <v>14300</v>
+      </c>
+      <c r="F5" s="30">
+        <v>0.25</v>
+      </c>
+      <c r="G5" s="17">
+        <v>147000</v>
+      </c>
+      <c r="H5" s="16">
+        <v>14300</v>
+      </c>
+      <c r="I5" s="16">
+        <v>14300</v>
+      </c>
+      <c r="J5" s="22">
+        <v>1</v>
+      </c>
+      <c r="K5" s="22">
+        <v>2015</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="N5" s="16">
+        <v>70</v>
+      </c>
+      <c r="O5" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="P5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="R5" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="S5" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="T5" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="U5" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="V5" s="22">
+        <v>1950</v>
+      </c>
+      <c r="W5" s="22">
+        <v>955</v>
+      </c>
+      <c r="X5" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y5" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="28">
+        <v>25000</v>
+      </c>
+      <c r="AA5" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB5" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="AC5" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD5" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE5" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF5" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG5" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AK5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN5" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AO5" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="AP5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ5" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR5" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="AS5" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="AT5" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="AU5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AV5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AW5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AX5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AY5" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="AZ5" s="17"/>
+    </row>
+    <row r="6" spans="1:52">
+      <c r="A6" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="18">
+        <v>11</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" s="16">
+        <v>14300</v>
+      </c>
+      <c r="F6" s="30">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="17">
+        <v>145000</v>
+      </c>
+      <c r="H6" s="16">
+        <v>14300</v>
+      </c>
+      <c r="I6" s="16">
+        <v>14300</v>
+      </c>
+      <c r="J6" s="22">
+        <v>1</v>
+      </c>
+      <c r="K6" s="22">
+        <v>2015</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="N6" s="16">
+        <v>70</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="P6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>0</v>
+      </c>
+      <c r="R6" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="S6" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="T6" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="U6" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="V6" s="22">
+        <v>1950</v>
+      </c>
+      <c r="W6" s="22">
+        <v>975</v>
+      </c>
+      <c r="X6" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y6" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="28">
+        <v>25000</v>
+      </c>
+      <c r="AA6" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB6" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="AC6" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD6" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE6" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF6" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG6" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH6" s="17" t="s">
+        <v>130</v>
+      </c>
       <c r="AI6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN6" s="17" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO6" s="17" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ6" s="17" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR6" s="17" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS6" s="17" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT6" s="17" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ6" s="17"/>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" s="12"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -53272,343 +52798,342 @@
     <col min="2" max="2" width="25.2857142857143" customWidth="1"/>
     <col min="3" max="3" width="23.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="27.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="14.4285714285714" customWidth="1"/>
-    <col min="7" max="7" width="12.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="14.4285714285714" style="6" customWidth="1"/>
     <col min="16" max="16" width="26" customWidth="1"/>
     <col min="27" max="27" width="24.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="142.5" spans="1:52">
       <c r="A1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="AR1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="AS1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="AT1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="AU1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="AV1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="AW1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="AX1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="AY1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="K1" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P1" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q1" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="U1" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="V1" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="W1" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="X1" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y1" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z1" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB1" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC1" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD1" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE1" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF1" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG1" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH1" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="AI1" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ1" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK1" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL1" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM1" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN1" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="AO1" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP1" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ1" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR1" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS1" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AT1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="AU1" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="AV1" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="AW1" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="AX1" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="AY1" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="AZ1" s="7" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:52">
       <c r="A2" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="O2" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="U2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="V2" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="W2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA2" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB2" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC2" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD2" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE2" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF2" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG2" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH2" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI2" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK2" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="AL2" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="AN2" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="AO2" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AP2" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ2" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="AR2" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="AS2" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="AT2" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="AU2" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="AV2" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="AW2" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="AX2" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="AY2" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="J2" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="U2" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="V2" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y2" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z2" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA2" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB2" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC2" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="AD2" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE2" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="AF2" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG2" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH2" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="AI2" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ2" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="AK2" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="AL2" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="AM2" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="AN2" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="AO2" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="AP2" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AQ2" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="AR2" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="AS2" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="AT2" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="AU2" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="AV2" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="AW2" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="AX2" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="AY2" s="12" t="s">
-        <v>154</v>
-      </c>
       <c r="AZ2" s="12" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:52">
       <c r="A3" s="15" t="s">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="E3" s="16">
         <v>14300</v>
       </c>
-      <c r="F3" s="30">
+      <c r="F3" s="14">
         <v>0.25</v>
       </c>
       <c r="G3" s="17">
@@ -53627,32 +53152,32 @@
         <v>2015</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N3" s="16">
         <v>70</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="P3" s="17" t="b">
         <v>0</v>
       </c>
       <c r="Q3" s="17"/>
       <c r="R3" s="23" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="S3" s="24" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T3" s="23" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U3" s="25" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="V3" s="22">
         <v>1950</v>
@@ -53661,7 +53186,7 @@
         <v>850</v>
       </c>
       <c r="X3" s="17" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y3" s="27">
         <v>1</v>
@@ -53670,97 +53195,97 @@
         <v>25000</v>
       </c>
       <c r="AA3" s="29" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB3" s="15" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="AC3" s="22" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD3" s="17" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE3" s="17" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF3" s="17" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG3" s="17" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN3" s="17" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO3" s="17" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ3" s="17" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR3" s="17" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS3" s="17" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT3" s="17" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY3" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ3" s="17"/>
     </row>
     <row r="4" spans="1:52">
       <c r="A4" s="15" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="13" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="E4" s="16">
         <v>14300</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="14">
         <v>0.25</v>
       </c>
       <c r="G4" s="17">
@@ -53779,32 +53304,32 @@
         <v>2015</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N4" s="16">
         <v>70</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="P4" s="17" t="b">
         <v>0</v>
       </c>
       <c r="Q4" s="17"/>
       <c r="R4" s="24" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="S4" s="24" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T4" s="24" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U4" s="26" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="V4" s="22">
         <v>1947</v>
@@ -53813,7 +53338,7 @@
         <v>900</v>
       </c>
       <c r="X4" s="17" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y4" s="27">
         <v>1</v>
@@ -53822,97 +53347,97 @@
         <v>25000</v>
       </c>
       <c r="AA4" s="29" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="AC4" s="22" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD4" s="17" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE4" s="17" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF4" s="17" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG4" s="17" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN4" s="17" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO4" s="17" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ4" s="17" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR4" s="17" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS4" s="17" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT4" s="17" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY4" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ4" s="17"/>
     </row>
     <row r="5" spans="1:52">
       <c r="A5" s="15" t="s">
-        <v>248</v>
+        <v>213</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="13" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="E5" s="16">
         <v>14300</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="14">
         <v>0.25</v>
       </c>
       <c r="G5" s="17">
@@ -53931,34 +53456,34 @@
         <v>2015</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N5" s="16">
         <v>70</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="P5" s="17" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="R5" s="23" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T5" s="23" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U5" s="25" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="V5" s="22">
         <v>1950</v>
@@ -53967,7 +53492,7 @@
         <v>955</v>
       </c>
       <c r="X5" s="17" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y5" s="27">
         <v>1</v>
@@ -53976,99 +53501,99 @@
         <v>25000</v>
       </c>
       <c r="AA5" s="29" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB5" s="15" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="AC5" s="22" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD5" s="17" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE5" s="17" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF5" s="17" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG5" s="17" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN5" s="17" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO5" s="17" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ5" s="17" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR5" s="17" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS5" s="17" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT5" s="17" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY5" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ5" s="17"/>
     </row>
     <row r="6" spans="1:52">
       <c r="A6" s="15" t="s">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="C6" s="18">
         <v>11</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="E6" s="16">
         <v>14300</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="14">
         <v>0.25</v>
       </c>
       <c r="G6" s="17">
@@ -54087,16 +53612,16 @@
         <v>2015</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="N6" s="16">
         <v>70</v>
       </c>
       <c r="O6" s="16" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="P6" s="17" t="b">
         <v>0</v>
@@ -54105,16 +53630,16 @@
         <v>0</v>
       </c>
       <c r="R6" s="23" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="T6" s="23" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="V6" s="22">
         <v>1950</v>
@@ -54123,7 +53648,7 @@
         <v>975</v>
       </c>
       <c r="X6" s="17" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="Y6" s="27">
         <v>1</v>
@@ -54132,79 +53657,79 @@
         <v>25000</v>
       </c>
       <c r="AA6" s="29" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="AB6" s="15" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="AC6" s="22" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AD6" s="17" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="AE6" s="17" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="AF6" s="17" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="AG6" s="17" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="AH6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AI6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AJ6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AK6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AN6" s="17" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="AO6" s="17" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="AP6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AQ6" s="17" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="AR6" s="17" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="AS6" s="17" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="AT6" s="17" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="AU6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AV6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AW6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AX6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AY6" s="17" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AZ6" s="17"/>
     </row>
@@ -54225,957 +53750,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AZ7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
-  <cols>
-    <col min="1" max="1" width="44.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="25.2857142857143" customWidth="1"/>
-    <col min="3" max="3" width="23.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="27.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="14.4285714285714" style="6" customWidth="1"/>
-    <col min="16" max="16" width="26" customWidth="1"/>
-    <col min="27" max="27" width="24.5714285714286" customWidth="1"/>
-  </cols>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="142.5" spans="1:52">
-      <c r="A1" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J1" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="K1" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="P1" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q1" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="U1" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="V1" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="W1" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="X1" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y1" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z1" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB1" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC1" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD1" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE1" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF1" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG1" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AH1" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="AI1" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ1" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AK1" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL1" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM1" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN1" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="AO1" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP1" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AQ1" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="AR1" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS1" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AT1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="AU1" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="AV1" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="AW1" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="AX1" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="AY1" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="AZ1" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:52">
-      <c r="A2" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="P2" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="U2" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="V2" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y2" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="Z2" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA2" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="AB2" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC2" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="AD2" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="AE2" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="AF2" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="AG2" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH2" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="AI2" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ2" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="AK2" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="AL2" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="AM2" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="AN2" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="AO2" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="AP2" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="AQ2" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="AR2" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="AS2" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="AT2" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="AU2" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="AV2" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="AW2" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="AX2" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="AY2" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="AZ2" s="12" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:52">
-      <c r="A3" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="E3" s="16">
-        <v>14300</v>
-      </c>
-      <c r="F3" s="14">
-        <v>0.25</v>
-      </c>
-      <c r="G3" s="17">
-        <v>143000</v>
-      </c>
-      <c r="H3" s="16">
-        <v>14300</v>
-      </c>
-      <c r="I3" s="16">
-        <v>14300</v>
-      </c>
-      <c r="J3" s="22">
-        <v>1</v>
-      </c>
-      <c r="K3" s="22">
-        <v>2015</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="M3" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="N3" s="16">
-        <v>70</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="P3" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="S3" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="T3" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="U3" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="V3" s="22">
-        <v>1950</v>
-      </c>
-      <c r="W3" s="22">
-        <v>850</v>
-      </c>
-      <c r="X3" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y3" s="27">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="28">
-        <v>25000</v>
-      </c>
-      <c r="AA3" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="AB3" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="AC3" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD3" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE3" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="AF3" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG3" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="AH3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AL3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AM3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN3" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="AO3" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="AP3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ3" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="AR3" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="AS3" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="AT3" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="AU3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AX3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ3" s="17"/>
-    </row>
-    <row r="4" spans="1:52">
-      <c r="A4" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="E4" s="16">
-        <v>14300</v>
-      </c>
-      <c r="F4" s="14">
-        <v>0.25</v>
-      </c>
-      <c r="G4" s="17">
-        <v>146000</v>
-      </c>
-      <c r="H4" s="16">
-        <v>14300</v>
-      </c>
-      <c r="I4" s="16">
-        <v>14300</v>
-      </c>
-      <c r="J4" s="22">
-        <v>1</v>
-      </c>
-      <c r="K4" s="22">
-        <v>2015</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="M4" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="N4" s="16">
-        <v>70</v>
-      </c>
-      <c r="O4" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="S4" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="T4" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="U4" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="V4" s="22">
-        <v>1947</v>
-      </c>
-      <c r="W4" s="22">
-        <v>900</v>
-      </c>
-      <c r="X4" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y4" s="27">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="28">
-        <v>25000</v>
-      </c>
-      <c r="AA4" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="AB4" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="AC4" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD4" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE4" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="AF4" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG4" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="AH4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AL4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AM4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN4" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="AO4" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="AP4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ4" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="AR4" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="AS4" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="AT4" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="AU4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AX4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ4" s="17"/>
-    </row>
-    <row r="5" spans="1:52">
-      <c r="A5" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E5" s="16">
-        <v>14300</v>
-      </c>
-      <c r="F5" s="14">
-        <v>0.25</v>
-      </c>
-      <c r="G5" s="17">
-        <v>147000</v>
-      </c>
-      <c r="H5" s="16">
-        <v>14300</v>
-      </c>
-      <c r="I5" s="16">
-        <v>14300</v>
-      </c>
-      <c r="J5" s="22">
-        <v>1</v>
-      </c>
-      <c r="K5" s="22">
-        <v>2015</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="M5" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="N5" s="16">
-        <v>70</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="P5" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>217</v>
-      </c>
-      <c r="R5" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="S5" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="T5" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="U5" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="V5" s="22">
-        <v>1950</v>
-      </c>
-      <c r="W5" s="22">
-        <v>955</v>
-      </c>
-      <c r="X5" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y5" s="27">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="28">
-        <v>25000</v>
-      </c>
-      <c r="AA5" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="AB5" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="AC5" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD5" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE5" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="AF5" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG5" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="AH5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AL5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AM5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN5" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="AO5" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="AP5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ5" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="AR5" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="AS5" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="AT5" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="AU5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AX5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ5" s="17"/>
-    </row>
-    <row r="6" spans="1:52">
-      <c r="A6" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="C6" s="18">
-        <v>11</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" s="16">
-        <v>14300</v>
-      </c>
-      <c r="F6" s="14">
-        <v>0.25</v>
-      </c>
-      <c r="G6" s="17">
-        <v>145000</v>
-      </c>
-      <c r="H6" s="16">
-        <v>14300</v>
-      </c>
-      <c r="I6" s="16">
-        <v>14300</v>
-      </c>
-      <c r="J6" s="22">
-        <v>1</v>
-      </c>
-      <c r="K6" s="22">
-        <v>2015</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="M6" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="N6" s="16">
-        <v>70</v>
-      </c>
-      <c r="O6" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="P6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>0</v>
-      </c>
-      <c r="R6" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="S6" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="T6" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="U6" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="V6" s="22">
-        <v>1950</v>
-      </c>
-      <c r="W6" s="22">
-        <v>975</v>
-      </c>
-      <c r="X6" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y6" s="27">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="28">
-        <v>25000</v>
-      </c>
-      <c r="AA6" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="AB6" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="AC6" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="AD6" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE6" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="AF6" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG6" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="AH6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AI6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AL6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AM6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN6" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="AO6" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="AP6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ6" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="AR6" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="AS6" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="AT6" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="AU6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AV6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AX6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY6" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ6" s="17"/>
-    </row>
-    <row r="7" spans="4:4">
-      <c r="D7" s="12"/>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>215</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O3:O6">
-      <formula1>"No,Yes"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -55184,12 +53767,53 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="1"/>
+  <cols>
+    <col min="2" max="2" width="28.4285714285714" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>254</v>
+        <v>215</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" spans="2:2">
+      <c r="B2" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
